--- a/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules a déjà joué un peu dans le salon. Ses jambes ont encore envie de bouger. Papa dit : on va dehors. Ils mettent les chaussures près de la porte. Ils prennent le ballon rouge. Ils vont au parc avec papa. Dehors, l'air est frais. Les oiseaux chantent. Jules court sur l'herbe. Papa reste près de lui. Jules lance le ballon. Papa le renvoie. Jules grimpe sur le petit muret. Papa le voit. Jules dit : je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.</t>
+          <t>Jules a déjà joué un peu dans le salon. Ses jambes ont encore envie de bouger. On va dehors. Ils mettent les chaussures près de la porte. Ils prennent le ballon rouge. Ils vont au parc avec papa. Dehors, l'air est frais. Les oiseaux chantent. Jules court sur l'herbe. Papa reste près de lui. Jules lance le ballon. Papa le renvoie. Jules grimpe sur le petit muret. Papa le voit. Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a déjà joué un peu dans le salon. Ses jambes ont encore envie de bouger.
+papa|On va dehors.
+narrateur|Ils mettent les chaussures près de la porte. Ils prennent le ballon rouge. Ils vont au parc avec papa. Dehors, l'air est frais. Les oiseaux chantent. Jules court sur l'herbe. Papa reste près de lui. Jules lance le ballon. Papa le renvoie. Jules grimpe sur le petit muret. Papa le voit.
+enfant-m|Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment.
+narrateur|Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jules veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules boit de l'eau. Il range le ballon. Merci, dit-il à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Jules veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Jules a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Jules boit de l'eau. Il range le ballon. Merci, dit-il à papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules joue au parc</t>
+          <t>Les lacets d'Aniss</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les lacets rouges pendent. Le ballon attend sous les manteaux. Aniss et papa vont au parc. Ils jouent dehors. Un adulte est là.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules a déjà joué un peu dans le salon. Ses jambes ont encore envie de bouger. On va dehors. Ils mettent les chaussures près de la porte. Ils prennent le ballon rouge. Ils vont au parc avec papa. Dehors, l'air est frais. Les oiseaux chantent. Jules court sur l'herbe. Papa reste près de lui. Jules lance le ballon. Papa le renvoie. Jules grimpe sur le petit muret. Papa le voit. Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.</t>
+          <t>Les lacets des baskets rouges pendent. Ils font deux petits vers. Le paillasson a encore de l'herbe. Le ballon rouge dort sous les manteaux. La porte sent le bois. Dehors, un oiseau appelle. En ce moment, les jambes d'Aniss gigotent. Papa. J'ai envie de bouger. On va dehors. Papa aide pour les lacets. Un nœud. Encore un nœud. Bravo. Tes pieds sont prêts. Ils prennent le ballon rouge. Il est un peu froid, un peu lisse. Ils marchent jusqu'au parc. L'air est frais. Les oiseaux chantent. Aniss court sur l'herbe. Papa reste près de lui. C'est un adulte. Aniss lance le ballon. Papa le renvoie. Le ballon fait poum. Encore ! Encore. Ils jouent un moment. Aniss grimpe sur le petit rondin. Papa le voit. Je joue dehors, avec un adulte. Bravo, Aniss. Tu bouges, et je suis là. Aniss sent son corps content. Ses joues sont chaudes. Puis ils rentrent ensemble. Aniss a bougé. Papa était là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules a déjà joué un peu dans le salon. Ses jambes ont encore envie de bouger.
+          <t>narrateur|Les lacets des baskets rouges pendent.
+narrateur|Ils font deux petits vers.
+narrateur|Le paillasson a encore de l'herbe.
+narrateur|Le ballon rouge dort sous les manteaux.
+narrateur|La porte sent le bois.
+narrateur|Dehors, un oiseau appelle.
+narrateur|En ce moment, les jambes d'Aniss gigotent.
+enfant-m|Papa.
+enfant-m|J'ai envie de bouger.
 papa|On va dehors.
-narrateur|Ils mettent les chaussures près de la porte. Ils prennent le ballon rouge. Ils vont au parc avec papa. Dehors, l'air est frais. Les oiseaux chantent. Jules court sur l'herbe. Papa reste près de lui. Jules lance le ballon. Papa le renvoie. Jules grimpe sur le petit muret. Papa le voit.
-enfant-m|Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment.
-narrateur|Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.</t>
+narrateur|Papa aide pour les lacets.
+narrateur|Un nœud.
+narrateur|Encore un nœud.
+papa|Bravo.
+papa|Tes pieds sont prêts.
+narrateur|Ils prennent le ballon rouge.
+narrateur|Il est un peu froid, un peu lisse.
+narrateur|Ils marchent jusqu'au parc.
+narrateur|L'air est frais.
+narrateur|Les oiseaux chantent.
+narrateur|Aniss court sur l'herbe.
+narrateur|Papa reste près de lui.
+narrateur|C'est un adulte.
+narrateur|Aniss lance le ballon.
+narrateur|Papa le renvoie.
+narrateur|Le ballon fait poum.
+enfant-m|Encore !
+papa|Encore.
+narrateur|Ils jouent un moment.
+narrateur|Aniss grimpe sur le petit rondin.
+narrateur|Papa le voit.
+enfant-m|Je joue dehors, avec un adulte.
+papa|Bravo, Aniss.
+papa|Tu bouges, et je suis là.
+narrateur|Aniss sent son corps content.
+narrateur|Ses joues sont chaudes.
+narrateur|Puis ils rentrent ensemble.
+narrateur|Aniss a bougé.
+narrateur|Papa était là.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,ballon</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jules veut bouger. Où joue-t-il ?</t>
+          <t>Aniss veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1555,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jules veut bouger. Où joue-t-il ?</t>
+          <t>narrateur|Aniss veut bouger.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+          <t>Aniss a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Tu as fait du bon travail. Dehors, avec un adulte. Oui, papa. Avec toi. Le ballon est un peu mouillé d'herbe. Aniss le serre. Il sent le caoutchouc. Tu as couru ? Oui. Beaucoup. Papa pose une main sur l'épaule. Elle est tiède. Les joues d'Aniss sont encore chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1728,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+          <t>narrateur|Aniss a joué dehors.
+narrateur|Papa, un adulte, était avec lui.
+narrateur|Le corps a bougé.
+narrateur|C'est bien.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Dehors, avec un adulte.
+enfant-m|Oui, papa.
+enfant-m|Avec toi.
+narrateur|Le ballon est un peu mouillé d'herbe.
+narrateur|Aniss le serre.
+narrateur|Il sent le caoutchouc.
+papa|Tu as couru ?
+enfant-m|Oui.
+enfant-m|Beaucoup.
+narrateur|Papa pose une main sur l'épaule.
+narrateur|Elle est tiède.
+narrateur|Les joues d'Aniss sont encore chaudes.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules boit de l'eau. Il range le ballon. Merci, dit-il à papa.</t>
+          <t>Aniss boit de l'eau. Le verre est frais. Il range le ballon. Le ballon retrouve sa place. Merci, papa. Merci, Aniss. Les lacets sont un peu verts, maintenant. De l'herbe. On les brosse à la maison. D'accord. Papa ouvre la porte. Ça sent encore le bois. Aniss enlève une basket. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1909,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules boit de l'eau. Il range le ballon. Merci, dit-il à papa.</t>
+          <t>narrateur|Aniss boit de l'eau.
+narrateur|Le verre est frais.
+narrateur|Il range le ballon.
+narrateur|Le ballon retrouve sa place.
+enfant-m|Merci, papa.
+papa|Merci, Aniss.
+narrateur|Les lacets sont un peu verts, maintenant.
+enfant-m|De l'herbe.
+papa|On les brosse à la maison.
+enfant-m|D'accord.
+narrateur|Papa ouvre la porte.
+narrateur|Ça sent encore le bois.
+narrateur|Aniss enlève une basket.
+narrateur|Puis l'autre.
+narrateur|Ses pieds sont contents.
+papa|On reste un peu ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Tu as fait du bon travail. Les lacets ont couru. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2093,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai joué dehors.
+enfant-m|Avec un adulte.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Les lacets ont couru.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les lacets des baskets rouges pendent. Ils font deux petits vers. Le paillasson a encore de l'herbe. Le ballon rouge dort sous les manteaux. La porte sent le bois. Dehors, un oiseau appelle. En ce moment, les jambes d'Aniss gigotent. Papa. J'ai envie de bouger. On va dehors. Papa aide pour les lacets. Un nœud. Encore un nœud. Bravo. Tes pieds sont prêts. Ils prennent le ballon rouge. Il est un peu froid, un peu lisse. Ils marchent jusqu'au parc. L'air est frais. Les oiseaux chantent. Aniss court sur l'herbe. Papa reste près de lui. C'est un adulte. Aniss lance le ballon. Papa le renvoie. Le ballon fait poum. Encore ! Encore. Ils jouent un moment. Aniss grimpe sur le petit rondin. Papa le voit. Je joue dehors, avec un adulte. Bravo, Aniss. Tu bouges, et je suis là. Aniss sent son corps content. Ses joues sont chaudes. Puis ils rentrent ensemble. Aniss a bougé. Papa était là.</t>
+          <t>Les lacets des baskets rouges pendent. Ils font deux petits vers. Le paillasson a encore de l'herbe. Une petite paille jaune. Le ballon rouge dort sous les manteaux. Un manteau bleu le cache un peu. La porte sent le bois. Dehors, un oiseau appelle. En ce moment, les jambes d'Aniss gigotent. Papa. J'ai envie de bouger. On va dehors. Papa aide pour les lacets. Un nœud. Encore un nœud. Bravo. Tes pieds sont prêts. Ils prennent le ballon rouge. Il est un peu froid, un peu lisse. Ils marchent jusqu'au parc. L'air est frais. Ça sent la terre humide. Les oiseaux chantent. Une flaque brille près du banc. Aniss court sur l'herbe. Papa reste près de lui. C'est un adulte. Aniss lance le ballon. Papa le renvoie. Le ballon fait poum. Encore ! Encore. Ils jouent un moment. Aniss grimpe sur le petit rondin. Le bois est rêche. Papa le voit. Je joue dehors, avec un adulte. Bravo, Aniss. Tu bouges, et je suis là. Tu as fini de lancer le ballon ? Encore un peu. Encore un peu, d'accord. Aniss sent son corps content. Ses joues sont chaudes. Puis ils rentrent ensemble. Aniss a bougé. Je suis avec toi. Oui, papa. Aniss donne la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a déjà joué un peu dans le salon. Ses jambes ont encore envie de bouger. Papa dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Ils mettent les chaussures près de la porte. Ils prennent le ballon rouge. Ils vont au parc avec papa. Dehors, l'air est frais. Les oiseaux chantent. Jules court sur l'herbe. Papa reste près de lui. Jules lance le ballon. Papa le renvoie. Jules grimpe sur le petit muret. Papa le voit. Jules dit : je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Jules sent son corps content. Puis ils rentrent ensemble. Jules a bougé. Papa était là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les lacets des baskets rouges pendent. Ils font deux petits vers. Le paillasson a encore de l'herbe. Une petite paille jaune. Le ballon rouge dort sous les manteaux. Un manteau bleu le cache un peu. La porte sent le bois. Dehors, un oiseau appelle. En ce moment, les jambes d'Aniss gigotent. Papa. J'ai envie de bouger. On va dehors. Papa aide pour les lacets. Un nœud. Encore un nœud. Bravo. Tes pieds sont prêts. Ils prennent le ballon rouge. Il est un peu froid, un peu lisse. Ils marchent jusqu'au parc. L'air est frais. Ça sent la terre humide. Les oiseaux chantent. Une flaque brille près du banc. Aniss court sur l'herbe. Papa reste près de lui. C'est un adulte. Aniss lance le ballon. Papa le renvoie. Le ballon fait poum. Encore ! Encore. Ils jouent un moment. Aniss grimpe sur le petit rondin. Le bois est rêche. Papa le voit. Je joue dehors, avec un adulte. Bravo, Aniss. Tu bouges, et je suis là. Tu as fini de lancer le ballon ? Encore un peu. Encore un peu, d'accord. Aniss sent son corps content. Ses joues sont chaudes. Puis ils rentrent ensemble. Aniss a bougé. Je suis avec toi. Oui, papa. Aniss donne la main.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1332,7 +1332,9 @@
           <t>narrateur|Les lacets des baskets rouges pendent.
 narrateur|Ils font deux petits vers.
 narrateur|Le paillasson a encore de l'herbe.
+narrateur|Une petite paille jaune.
 narrateur|Le ballon rouge dort sous les manteaux.
+narrateur|Un manteau bleu le cache un peu.
 narrateur|La porte sent le bois.
 narrateur|Dehors, un oiseau appelle.
 narrateur|En ce moment, les jambes d'Aniss gigotent.
@@ -1348,7 +1350,9 @@
 narrateur|Il est un peu froid, un peu lisse.
 narrateur|Ils marchent jusqu'au parc.
 narrateur|L'air est frais.
+narrateur|Ça sent la terre humide.
 narrateur|Les oiseaux chantent.
+narrateur|Une flaque brille près du banc.
 narrateur|Aniss court sur l'herbe.
 narrateur|Papa reste près de lui.
 narrateur|C'est un adulte.
@@ -1359,15 +1363,21 @@
 papa|Encore.
 narrateur|Ils jouent un moment.
 narrateur|Aniss grimpe sur le petit rondin.
+narrateur|Le bois est rêche.
 narrateur|Papa le voit.
 enfant-m|Je joue dehors, avec un adulte.
 papa|Bravo, Aniss.
 papa|Tu bouges, et je suis là.
+papa|Tu as fini de lancer le ballon ?
+enfant-m|Encore un peu.
+papa|Encore un peu, d'accord.
 narrateur|Aniss sent son corps content.
 narrateur|Ses joues sont chaudes.
 narrateur|Puis ils rentrent ensemble.
 narrateur|Aniss a bougé.
-narrateur|Papa était là.</t>
+papa|Je suis avec toi.
+enfant-m|Oui, papa.
+narrateur|Aniss donne la main.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1404,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules veut bouger. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1559,7 +1569,6 @@
 narrateur|Où joue-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1584,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Tu as fait du bon travail. Dehors, avec un adulte. Oui, papa. Avec toi. Le ballon est un peu mouillé d'herbe. Aniss le serre. Il sent le caoutchouc. Tu as couru ? Oui. Beaucoup. Papa pose une main sur l'épaule. Elle est tiède. Les joues d'Aniss sont encore chaudes.</t>
+          <t>Aniss a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Dehors, avec un adulte. Oui, papa. Avec toi. Le ballon est un peu mouillé d'herbe. Aniss le serre. Il sent le caoutchouc. Tu as couru ? Oui. Beaucoup. Papa pose une main sur l'épaule. Elle est tiède. Les joues d'Aniss sont encore chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien. Bravo. Dehors, avec un adulte. Oui, papa. Avec toi. Le ballon est un peu mouillé d'herbe. Aniss le serre. Il sent le caoutchouc. Tu as couru ? Oui. Beaucoup. Papa pose une main sur l'épaule. Elle est tiède. Les joues d'Aniss sont encore chaudes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1733,7 +1742,6 @@
 narrateur|Le corps a bougé.
 narrateur|C'est bien.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 papa|Dehors, avec un adulte.
 enfant-m|Oui, papa.
 enfant-m|Avec toi.
@@ -1748,7 +1756,6 @@
 narrateur|Les joues d'Aniss sont encore chaudes.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1773,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aniss boit de l'eau. Le verre est frais. Il range le ballon. Le ballon retrouve sa place. Merci, papa. Merci, Aniss. Les lacets sont un peu verts, maintenant. De l'herbe. On les brosse à la maison. D'accord. Papa ouvre la porte. Ça sent encore le bois. Aniss enlève une basket. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, papa.</t>
+          <t>Aniss boit de l'eau. Le verre est frais. Il range le ballon. Le ballon retrouve sa place. Merci, papa. Merci, Aniss. Les lacets sont un peu verts, maintenant. De l'herbe. On les brosse à la maison. D'accord. Papa ouvre la porte. Ça sent encore le bois. Aniss enlève une basket. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, papa. Le paillasson a encore de l'herbe. On enlève les baskets, tout doux. D'accord, papa. Les lacets reposent, enfin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules boit de l'eau. Il range le ballon. Merci, dit-il à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss boit de l'eau. Le verre est frais. Il range le ballon. Le ballon retrouve sa place. Merci, papa. Merci, Aniss. Les lacets sont un peu verts, maintenant. De l'herbe. On les brosse à la maison. D'accord. Papa ouvre la porte. Ça sent encore le bois. Aniss enlève une basket. Puis l'autre. Ses pieds sont contents. On reste un peu ? Oui, papa. Le paillasson a encore de l'herbe. On enlève les baskets, tout doux. D'accord, papa. Les lacets reposent, enfin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1925,10 +1932,13 @@
 narrateur|Puis l'autre.
 narrateur|Ses pieds sont contents.
 papa|On reste un peu ?
-enfant-m|Oui, papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+enfant-m|Oui, papa.
+narrateur|Le paillasson a encore de l'herbe.
+papa|On enlève les baskets, tout doux.
+enfant-m|D'accord, papa.
+narrateur|Les lacets reposent, enfin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai joué dehors. Avec un adulte. Bravo. Tu as fait du bon travail. Les lacets ont couru. L'histoire est finie.</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Les lacets ont couru.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Les lacets ont couru.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,12 +2106,9 @@
           <t>enfant-m|J'ai joué dehors.
 enfant-m|Avec un adulte.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-papa|Les lacets ont couru.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Les lacets ont couru.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-01.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
